--- a/00_Data/Datasets_metadata.xlsx
+++ b/00_Data/Datasets_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqfchar1_uq_edu_au/Documents/Desktop/GitHub/Fire_freq_pred_modelling/00_Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felicitycharles/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{72BB4C31-F3BE-4975-8146-F72EF8A5AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428AB144-1547-4C50-A38F-C44A7DE46131}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC7F1FA-A4A7-324A-8ABD-036C07783D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1020" windowWidth="28800" windowHeight="15370" xr2:uid="{CFB87D9E-A38C-4243-925E-2D890E6206AE}"/>
+    <workbookView xWindow="940" yWindow="1020" windowWidth="28800" windowHeight="15380" xr2:uid="{CFB87D9E-A38C-4243-925E-2D890E6206AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
   <si>
     <t>Dataset</t>
   </si>
@@ -83,9 +83,6 @@
     <t>QLD</t>
   </si>
   <si>
-    <t>https://qldspatial.information.qld.gov.au/catalogue/custom/detail.page?fid={07E360E3-A191-4C24-9671-1471362F0B1B}</t>
-  </si>
-  <si>
     <t>1930-2022</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>This dataset is derived from databases maintained by QPWS rangers and officers at park bases. Rangers use various techniques to capture the extent of fires including capturing on paper plans on site, digitising from aerial imagery, vegetation layers and other spatial information using Geographic Information System (GIS) software, capturing with devices that use the Global Position System (GPS) or capturing from fire scar analysis of satellite imagery. While for most records the information about the fire is captured at the time of the fire, records of historical fires have been placed into the dataset.</t>
   </si>
   <si>
-    <t>https://qldspatial.information.qld.gov.au/catalogue/custom/detail.page?fid=%7b607736AE-8F4C-4058-B97F-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2017-2022 </t>
   </si>
   <si>
@@ -158,9 +152,6 @@
     <t>https://doi.org/10.4225/08/57590B59A4A08</t>
   </si>
   <si>
-    <t>Solar radiation - total incoming downward shortwave radiation on a horizontal surface</t>
-  </si>
-  <si>
     <t>1889-2023</t>
   </si>
   <si>
@@ -170,9 +161,6 @@
     <t>5km</t>
   </si>
   <si>
-    <t>https://s3-ap-southeast-2.amazonaws.com/silo-open-data/Official/annual/index.html</t>
-  </si>
-  <si>
     <t>Landsat Foliage Projective Cover - Queensland 2014</t>
   </si>
   <si>
@@ -182,27 +170,6 @@
     <t>28/08/2023, redownloaded 17/04/2024</t>
   </si>
   <si>
-    <t>https://qldspatial.information.qld.gov.au/catalogue/custom/detail.page?fid={E3A795AC-867D-4AA2-96DA-FF6F7BC6F3CD}</t>
-  </si>
-  <si>
-    <t>WorldClim Bioclimatic variables</t>
-  </si>
-  <si>
-    <t>1970-2000</t>
-  </si>
-  <si>
-    <t>WorldClim</t>
-  </si>
-  <si>
-    <t>1km</t>
-  </si>
-  <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>https://www.worldclim.org/data/worldclim21.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">SRTM-derived 1 Second Digital Elevation Model - DEM </t>
   </si>
   <si>
@@ -224,9 +191,6 @@
     <t>Statewide Landcover and Trees Study (SLATS) Sentinel-2-2018 Foliage Projective Cover</t>
   </si>
   <si>
-    <t>https://qldspatial.information.qld.gov.au/catalogue/custom/search.page?q=tree+cover</t>
-  </si>
-  <si>
     <t>Statewide Landcover and Trees Study (SLATS) Sentinel-2-2019 Foliage Projective Cover</t>
   </si>
   <si>
@@ -309,6 +273,39 @@
   </si>
   <si>
     <t>100m</t>
+  </si>
+  <si>
+    <t>Daily rainfall</t>
+  </si>
+  <si>
+    <t>Daily minimum temperature</t>
+  </si>
+  <si>
+    <t>Daily maximum temperature</t>
+  </si>
+  <si>
+    <t>Landsat Foliage Projective Cover - Queensland 2012</t>
+  </si>
+  <si>
+    <t>Landsat Foliage Projective Cover - Queensland 2013</t>
+  </si>
+  <si>
+    <t>25m</t>
+  </si>
+  <si>
+    <t>1988-2012</t>
+  </si>
+  <si>
+    <t>1988-2013</t>
+  </si>
+  <si>
+    <t>Statewide Landcover and Trees Study (SLATS) Sentinel-2-2022 Foliage Projective Cover</t>
+  </si>
+  <si>
+    <t>Statewide Landcover and Trees Study (SLATS) Sentinel-2-2023 Foliage Projective Cover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://s3-ap-southeast-2.amazonaws.com/silo-open-data/Official/annual/index.html </t>
   </si>
 </sst>
 </file>
@@ -710,18 +707,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B4C87A-1EDD-4382-8DCB-38A5028796CA}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.90625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -747,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -764,7 +761,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -773,15 +770,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D3" s="2">
         <v>44585</v>
@@ -793,90 +790,90 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="231" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="231" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
       </c>
       <c r="D4" s="2">
         <v>45156</v>
       </c>
       <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="D5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="D6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -888,21 +885,21 @@
         <v>45054</v>
       </c>
       <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -914,21 +911,21 @@
         <v>45054</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -940,21 +937,21 @@
         <v>45054</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -966,21 +963,21 @@
         <v>45054</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -992,105 +989,105 @@
         <v>45156</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2">
-        <v>45156</v>
+        <v>45399</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>86</v>
+      </c>
+      <c r="D13" s="2">
+        <v>45399</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
-      <c r="C14">
-        <v>2018</v>
-      </c>
-      <c r="D14" s="2">
-        <v>45398</v>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D15" s="2">
         <v>45398</v>
@@ -1099,24 +1096,24 @@
         <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D16" s="2">
         <v>45398</v>
@@ -1125,21 +1122,24 @@
         <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D17" s="2">
         <v>45398</v>
@@ -1148,154 +1148,145 @@
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>2021</v>
+      </c>
+      <c r="D18" s="2">
+        <v>45398</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19">
+        <v>2022</v>
+      </c>
+      <c r="D19" s="2">
+        <v>45398</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20">
+        <v>2023</v>
+      </c>
+      <c r="D20" s="2">
+        <v>45398</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45217</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>2021</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45394</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="2">
-        <v>45166</v>
-      </c>
-      <c r="E18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" t="s">
+    </row>
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="2">
-        <v>45217</v>
-      </c>
-      <c r="E19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20">
-        <v>2021</v>
-      </c>
-      <c r="D20" s="2">
-        <v>45394</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="2">
-        <v>45413</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="2">
-        <v>45413</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2">
         <v>45413</v>
@@ -1304,24 +1295,24 @@
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
       </c>
-      <c r="H23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H23" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2">
         <v>45413</v>
@@ -1330,24 +1321,24 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D25" s="2">
         <v>45413</v>
@@ -1356,101 +1347,230 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D26" s="2">
-        <v>45665</v>
+        <v>45413</v>
       </c>
       <c r="E26" t="s">
         <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
-      <c r="C27">
-        <v>2024</v>
+      <c r="C27" t="s">
+        <v>65</v>
       </c>
       <c r="D27" s="2">
-        <v>45665</v>
+        <v>45413</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G27" t="s">
         <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D28" s="2">
         <v>45665</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29">
+        <v>2024</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45665</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="2">
+        <v>45665</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="2">
+        <v>45868</v>
+      </c>
+      <c r="E31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45868</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+      <c r="F32" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="2">
+        <v>45868</v>
+      </c>
+      <c r="E33" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H19" r:id="rId1" location="/metadata/72759" xr:uid="{8F574A9D-6A61-454F-A85D-667CB68B127C}"/>
-    <hyperlink ref="H14" r:id="rId2" xr:uid="{F9FE474F-6DE4-4740-9DA3-3FF75D744024}"/>
-    <hyperlink ref="H15" r:id="rId3" xr:uid="{3AEEDBB4-6750-4A33-8636-422B381767F6}"/>
-    <hyperlink ref="H16" r:id="rId4" xr:uid="{92A3C4B3-BB71-42E5-AA60-0DBCF797E66E}"/>
-    <hyperlink ref="H17" r:id="rId5" xr:uid="{35790506-D8AA-4DF7-873B-9BC393B89E46}"/>
-    <hyperlink ref="H21" r:id="rId6" xr:uid="{48324849-A630-42B9-A28A-1F0DD76CDA57}"/>
+    <hyperlink ref="H21" r:id="rId1" location="/metadata/72759" xr:uid="{8F574A9D-6A61-454F-A85D-667CB68B127C}"/>
+    <hyperlink ref="H23" r:id="rId2" xr:uid="{48324849-A630-42B9-A28A-1F0DD76CDA57}"/>
+    <hyperlink ref="H31" r:id="rId3" display="https://s3-ap-southeast-2.amazonaws.com/silo-open-data/Official/annual/index.html" xr:uid="{F311D411-37D8-9F4C-9C68-8A8BE30E07BA}"/>
+    <hyperlink ref="H32" r:id="rId4" display="https://s3-ap-southeast-2.amazonaws.com/silo-open-data/Official/annual/index.html" xr:uid="{E7D224CD-AB32-3A4A-AB9B-4A52992B764E}"/>
+    <hyperlink ref="H33" r:id="rId5" display="https://s3-ap-southeast-2.amazonaws.com/silo-open-data/Official/annual/index.html" xr:uid="{61A9BE20-1243-1347-A36E-56D7A8ACD633}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/00_Data/Datasets_metadata.xlsx
+++ b/00_Data/Datasets_metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felicitycharles/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felicitycharles/Desktop/GitHub/Fire_freq_pred_modelling/00_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC7F1FA-A4A7-324A-8ABD-036C07783D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBAF504-660F-FC4F-AD7B-3166D87CEF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="1020" windowWidth="28800" windowHeight="15380" xr2:uid="{CFB87D9E-A38C-4243-925E-2D890E6206AE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="90">
   <si>
     <t>Dataset</t>
   </si>
@@ -1161,6 +1161,9 @@
       <c r="A18" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
       <c r="C18">
         <v>2021</v>
       </c>
@@ -1184,6 +1187,9 @@
       <c r="A19" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
       <c r="C19">
         <v>2022</v>
       </c>
@@ -1206,6 +1212,9 @@
     <row r="20" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>88</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
       </c>
       <c r="C20">
         <v>2023</v>
